--- a/artfynd/S 686-2024 artfynd.xlsx
+++ b/artfynd/S 686-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137365950</v>
       </c>
       <c r="B2" t="n">
-        <v>80052</v>
+        <v>80057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 686-2024 artfynd.xlsx
+++ b/artfynd/S 686-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137365950</v>
       </c>
       <c r="B2" t="n">
-        <v>80057</v>
+        <v>80068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 686-2024 artfynd.xlsx
+++ b/artfynd/S 686-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137365950</v>
       </c>
       <c r="B2" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 686-2024 artfynd.xlsx
+++ b/artfynd/S 686-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137365950</v>
       </c>
       <c r="B2" t="n">
-        <v>80069</v>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 686-2024 artfynd.xlsx
+++ b/artfynd/S 686-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137365950</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
